--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="170">
   <si>
     <t>id</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+  </si>
+  <si>
+    <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","fx":{"img":"🔥"}}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火球術",
@@ -1454,20 +1457,22 @@
       <c r="F2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="H2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1476,18 +1481,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>78</v>
@@ -1499,25 +1507,27 @@
         <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1526,24 +1536,27 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>33</v>
@@ -1552,16 +1565,19 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="8:9" x14ac:dyDescent="0.25">
@@ -1626,10 +1642,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1638,22 +1654,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1662,21 +1678,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1685,24 +1701,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1711,16 +1727,16 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1790,10 +1806,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1802,22 +1818,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1826,21 +1842,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1849,16 +1865,16 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1934,98 +1950,98 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -2094,10 +2110,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2107,18 +2123,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2127,18 +2143,18 @@
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2148,10 +2164,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -368,7 +368,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6,"scope":"area","radius":3,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135},"fx":{"img":"🔥"}</t>
+    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6,"scope":"area","radius":3,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="171">
   <si>
     <t>id</t>
   </si>
@@ -293,7 +293,7 @@
     <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
   </si>
   <si>
-    <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","fx":{"img":"🔥"}}</t>
+    <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","fx":{"img":"🔥"},"stack":3}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火球術",
@@ -310,7 +310,10 @@
     <t>🧱</t>
   </si>
   <si>
-    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"icons:1","scl":1,"deg":-45},"fx":{}</t>
+    <t>summon</t>
+  </si>
+  <si>
+    <t>"cd":3,"range":5,"cast":{},"zoneRadius":1,"zoneDur":4,"zoneImg":"🔥"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火牆術",
@@ -1478,24 +1481,24 @@
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>78</v>
@@ -1507,27 +1510,27 @@
         <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1536,27 +1539,27 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>33</v>
@@ -1565,19 +1568,19 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="8:9" x14ac:dyDescent="0.25">
@@ -1642,10 +1645,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1654,22 +1657,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1678,21 +1681,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1701,24 +1704,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1727,16 +1730,16 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1806,10 +1809,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1818,22 +1821,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1842,21 +1845,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1865,16 +1868,16 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1950,98 +1953,98 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -2110,10 +2113,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2123,18 +2126,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2143,18 +2146,18 @@
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2164,10 +2167,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -175,7 +175,7 @@
     <t>"slash","thrust"</t>
   </si>
   <si>
-    <t>"range":1,"cd":3,"scope":"group","radius":1,"cast":{},"fx":{}</t>
+    <t>"range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
@@ -313,7 +313,7 @@
     <t>summon</t>
   </si>
   <si>
-    <t>"cd":3,"range":5,"cast":{},"zoneRadius":1,"zoneDur":4,"zoneImg":"🔥"</t>
+    <t>"cd":3,"range":5,"cast":{},"zoneW":5,"zoneH":1,"zoneDur":4,"zoneImg":"🔥"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火牆術",
@@ -330,7 +330,7 @@
     <t>"fireball"</t>
   </si>
   <si>
-    <t>"scope":"group","radius":2,"pow":1.8,"flat":10,"elm":"fire","src":"int","cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+    <t>"scope":"group","w":5,"h":5,"pow":1.8,"flat":10,"elm":"fire","src":"int","cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"高級火球術",
@@ -351,7 +351,7 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2,"cast":{},"fx":{}</t>
+    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","w":5,"h":5,"cast":{},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",
@@ -371,7 +371,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6,"scope":"area","radius":3,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
+    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"pow":1.15,"flat":0,"range":1,"cd":1,"travel":{"type":"melee"}</t>
+    <t>"hits":[{"pow":1.15,"flat":0}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
@@ -155,7 +155,7 @@
     <t>📍</t>
   </si>
   <si>
-    <t>"pow":1.0,"flat":0,"pen":0.2,"range":1,"cd":1,"travel":{"type":"melee"}</t>
+    <t>"hits":[{"pow":1.0,"flat":0,"pen":0.2}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"刺擊",
@@ -179,11 +179,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
-"des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
+"des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Whirlwind",
-"des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
+"des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
   </si>
   <si>
     <t>swordmastery</t>
@@ -234,7 +234,7 @@
     <t>🎯</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":0,"range":5,"cd":3,"travel":{"type":"ranged"}</t>
+    <t>"hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",
@@ -290,18 +290,18 @@
     <t>🔥</t>
   </si>
   <si>
-    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
-  </si>
-  <si>
-    <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","fx":{"img":"🔥"},"stack":3}</t>
+    <t>"scope":"single","cd":3,"range":5,"hits":[{"elm":"fire","pow":1.5,"flat":10,"src":"int"}],"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+  </si>
+  <si>
+    <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","stack":3}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火球術",
-"des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
+"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Fireball",
-"des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
+"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
   </si>
   <si>
     <t>firewall</t>
@@ -313,15 +313,15 @@
     <t>summon</t>
   </si>
   <si>
-    <t>"cd":3,"range":5,"cast":{},"zoneW":5,"zoneH":1,"zoneDur":4,"zoneImg":"🔥"</t>
+    <t>"cd":3,"range":5,"cast":{},"zoneW":5,"zoneH":1,"zoneDur":4,"zoneImg":"🔥","zoneAnim":{"cell":{"size":30,"jitter":3,"scale":[0.85,1.15],"alpha":0.9,"flipX":"random"},"spawn":{"scale":{"from":0,"to":1},"duration":250,"ease":"Back.Out","stagger":70,"from":"center"},"idle":{"scaleX":{"from":0.75,"to":1.25},"scaleY":{"from":0.75,"to":1.25},"y":"-=2","duration":450,"yoyo":true,"repeat":-1,"ease":"Sine.InOut","randDelay":450},"tick":{"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"},"end":{"alpha":0,"scale":0.3,"duration":350,"ease":"Quad.In"}}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火牆術",
-"des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
+"des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Fire Wall",
-"des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
+"des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
     <t>fireballvolley</t>
@@ -330,15 +330,15 @@
     <t>"fireball"</t>
   </si>
   <si>
-    <t>"scope":"group","w":5,"h":5,"pow":1.8,"flat":10,"elm":"fire","src":"int","cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+    <t>"scope":"group","w":5,"h":5,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"高級火球術",
-"des":"對自身周圍範圍內的敵人各自發射火球，造成範圍傷害。"</t>
+"des":"對自身周圍範圍{#wh}方格內的敵人各自發射火球，每發造成 {#fmt} 點{#elm}傷害({#formula})。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Greater Fireball",
-"des":"Fires a fireball at each enemy within range around yourself."</t>
+"des":"Fires a fireball at each enemy within a {#wh} tile range around yourself, dealing {#fmt} {#elm} damage each ({#formula})."</t>
   </si>
   <si>
     <t>combustion</t>
@@ -351,15 +351,15 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","w":5,"h":5,"cast":{},"fx":{}</t>
+    <t>"range":5,"hits":[{"elm":"fire","pow":2.0,"flat":15,"src":"int"}],"cd":4,"scope":"group","w":5,"h":5,"cast":{},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",
-"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
+"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Combustion",
-"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
+"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
   </si>
   <si>
     <t>meteorshower</t>
@@ -371,15 +371,15 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
+    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",
-"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
+"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Meteor Shower",
-"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
+"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
   </si>
   <si>
     <t>icebolt</t>
@@ -388,7 +388,7 @@
     <t>❄️</t>
   </si>
   <si>
-    <t>"pow":1.5,"flat":10,"elm":"ice","src":"int","range":5,"cd":3</t>
+    <t>"hits":[{"elm":"ice","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"冰箭術",
@@ -423,7 +423,7 @@
 "icewall"</t>
   </si>
   <si>
-    <t>"pow":2.0,"flat":15,"elm":"ice","src":"int","range":5,"cd":4</t>
+    <t>"hits":[{"elm":"ice","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"冰封術",
@@ -443,7 +443,7 @@
     <t>"deepfreeze"</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":20,"elm":"ice","src":"int","range":5,"cd":6</t>
+    <t>"hits":[{"elm":"ice","pow":2.5,"flat":20,"src":"int"}],"range":5,"cd":6</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"暴風雪",
@@ -460,7 +460,7 @@
     <t>🐍</t>
   </si>
   <si>
-    <t>"pow":1.5,"flat":10,"elm":"poison","src":"int","range":5,"cd":3</t>
+    <t>"hits":[{"elm":"poison","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"毒箭術",
@@ -487,7 +487,7 @@
 "poisonmist"</t>
   </si>
   <si>
-    <t>"pow":2.0,"flat":15,"elm":"poison","src":"int","range":5,"cd":4</t>
+    <t>"hits":[{"elm":"poison","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"毒素引爆",
@@ -1032,6 +1032,7 @@
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1053,6 +1054,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="2"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1070,6 +1072,7 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1098,11 +1101,11 @@
     <row r="7" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="G13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1169,6 +1172,7 @@
       <c r="F2" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>36</v>
       </c>
@@ -1192,6 +1196,7 @@
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>41</v>
       </c>
@@ -1218,6 +1223,7 @@
       <c r="F4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>47</v>
       </c>
@@ -1338,6 +1344,7 @@
       <c r="F2" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>64</v>
       </c>
@@ -1409,7 +1416,7 @@
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="59.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="101" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
@@ -1470,7 +1477,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" ht="105" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -1587,11 +1594,11 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+    <row r="14" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="G14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1683,6 +1690,7 @@
       <c r="F3" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>113</v>
       </c>
@@ -1709,6 +1717,7 @@
       <c r="F4" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>119</v>
       </c>
@@ -1735,6 +1744,7 @@
       <c r="F5" s="2" t="s">
         <v>124</v>
       </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="2" t="s">
         <v>125</v>
       </c>
@@ -1751,11 +1761,11 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="G13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1847,6 +1857,7 @@
       <c r="F3" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>133</v>
       </c>
@@ -1873,6 +1884,7 @@
       <c r="F4" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>138</v>
       </c>
@@ -1894,11 +1906,11 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="G13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1991,6 +2003,7 @@
       <c r="F3" s="2" t="s">
         <v>146</v>
       </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>147</v>
       </c>
@@ -2014,6 +2027,7 @@
       <c r="F4" s="2" t="s">
         <v>146</v>
       </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>151</v>
       </c>
@@ -2040,6 +2054,7 @@
       <c r="F5" s="2" t="s">
         <v>156</v>
       </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="2" t="s">
         <v>157</v>
       </c>
@@ -2056,11 +2071,11 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="G13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2145,6 +2160,7 @@
       <c r="D3" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>165</v>
       </c>
@@ -2166,6 +2182,7 @@
         <v>51</v>
       </c>
       <c r="E4" s="2"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>169</v>
       </c>
@@ -2182,11 +2199,11 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+    <row r="12" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="G12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -330,15 +330,15 @@
     <t>"fireball"</t>
   </si>
   <si>
-    <t>"scope":"group","w":5,"h":5,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+    <t>"scope":"cone","range":5,"angle":45,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"高級火球術",
-"des":"對自身周圍範圍{#wh}方格內的敵人各自發射火球，每發造成 {#fmt} 點{#elm}傷害({#formula})。"</t>
+"des":"朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害({#formula})。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Greater Fireball",
-"des":"Fires a fireball at each enemy within a {#wh} tile range around yourself, dealing {#fmt} {#elm} damage each ({#formula})."</t>
+"des":"Fires a fireball at each character within a {#angle}° cone up to {#range} tiles in the chosen direction, dealing {#fmt} {#elm} damage each ({#formula})."</t>
   </si>
   <si>
     <t>combustion</t>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="750" yWindow="1185" windowWidth="19200" windowHeight="6450" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="general" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="sword" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="archery" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="fire" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="ice" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="poison" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="support" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="enhancement" state="visible" r:id="rId11"/>
+    <sheet name="general" sheetId="1" r:id="rId1"/>
+    <sheet name="sword" sheetId="2" r:id="rId2"/>
+    <sheet name="archery" sheetId="3" r:id="rId3"/>
+    <sheet name="fire" sheetId="4" r:id="rId4"/>
+    <sheet name="ice" sheetId="5" r:id="rId5"/>
+    <sheet name="poison" sheetId="6" r:id="rId6"/>
+    <sheet name="support" sheetId="7" r:id="rId7"/>
+    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -59,11 +59,11 @@
     <t>passive</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"偷竊",
+    <t>"lab":"偷竊",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Stealing",
+    <t>"lab":"Stealing",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
@@ -73,11 +73,11 @@
     <t>🗝️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"開鎖",
+    <t>"lab":"開鎖",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Lockpicking",
+    <t>"lab":"Lockpicking",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
@@ -87,11 +87,11 @@
     <t>🔪</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"解剖",
+    <t>"lab":"解剖",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Butcher",
+    <t>"lab":"Butcher",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
@@ -101,11 +101,11 @@
     <t>👤</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"潛行",
+    <t>"lab":"潛行",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Stealth",
+    <t>"lab":"Stealth",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
@@ -115,11 +115,11 @@
     <t>💰</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"討價還價",
+    <t>"lab":"討價還價",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Barter",
+    <t>"lab":"Barter",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
@@ -141,11 +141,11 @@
     <t>"hits":[{"pow":1.15,"flat":0}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"斬擊",
+    <t>"lab":"斬擊",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Slash",
+    <t>"lab":"Slash",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
@@ -158,11 +158,11 @@
     <t>"hits":[{"pow":1.0,"flat":0,"pen":0.2}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"刺擊",
+    <t>"lab":"刺擊",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Thrust",
+    <t>"lab":"Thrust",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
   <si>
@@ -178,11 +178,11 @@
     <t>"range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"旋風斬",
+    <t>"lab":"旋風斬",
 "des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Whirlwind",
+    <t>"lab":"Whirlwind",
 "des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
   </si>
   <si>
@@ -195,15 +195,15 @@
     <t>buff</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
+    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"劍術專家",
+    <t>"lab":"劍術專家",
 "des":"精通劍術。裝備劍類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Sword Expertise",
+    <t>"lab":"Sword Expertise",
 "des":"Mastery of swordsmanship. +10% accuracy and +10% attack power while wielding a sword."</t>
   </si>
   <si>
@@ -216,15 +216,15 @@
     <t>"swordmastery"</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
+    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"劍術大師",
+    <t>"lab":"劍術大師",
 "des":"劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Sword Mastery",
+    <t>"lab":"Sword Mastery",
 "des":"Peak swordsmanship. Further boosts accuracy and attack power while wielding a sword."</t>
   </si>
   <si>
@@ -237,11 +237,11 @@
     <t>"hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"狙擊",
+    <t>"lab":"狙擊",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Snipe",
+    <t>"lab":"Snipe",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
@@ -251,15 +251,15 @@
     <t>🏹</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
+    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓箭專家",
+    <t>"lab":"弓箭專家",
 "des":"精通弓術。裝備弓類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Archery Expertise",
+    <t>"lab":"Archery Expertise",
 "des":"Mastery of archery. +10% accuracy and +10% attack power while wielding a bow."</t>
   </si>
   <si>
@@ -272,15 +272,15 @@
     <t>"archeryexpert"</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
+    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓箭大師",
+    <t>"lab":"弓箭大師",
 "des":"弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Archery Mastery",
+    <t>"lab":"Archery Mastery",
 "des":"Peak archery. Further boosts accuracy and attack power while wielding a bow."</t>
   </si>
   <si>
@@ -296,11 +296,11 @@
     <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","stack":3}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"火球術",
+    <t>"lab":"火球術",
 "des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Fireball",
+    <t>"lab":"Fireball",
 "des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
   </si>
   <si>
@@ -316,11 +316,11 @@
     <t>"cd":3,"range":5,"cast":{},"zoneW":5,"zoneH":1,"zoneDur":4,"zoneImg":"🔥","zoneAnim":{"cell":{"size":30,"jitter":3,"scale":[0.85,1.15],"alpha":0.9,"flipX":"random"},"spawn":{"scale":{"from":0,"to":1},"duration":250,"ease":"Back.Out","stagger":70,"from":"center"},"idle":{"scaleX":{"from":0.75,"to":1.25},"scaleY":{"from":0.75,"to":1.25},"y":"-=2","duration":450,"yoyo":true,"repeat":-1,"ease":"Sine.InOut","randDelay":450},"tick":{"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"},"end":{"alpha":0,"scale":0.3,"duration":350,"ease":"Quad.In"}}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"火牆術",
+    <t>"lab":"火牆術",
 "des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Fire Wall",
+    <t>"lab":"Fire Wall",
 "des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
@@ -330,14 +330,11 @@
     <t>"fireball"</t>
   </si>
   <si>
-    <t>"scope":"cone","range":5,"angle":45,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"高級火球術",
+    <t>"lab":"高級火球術",
 "des":"朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害({#formula})。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Greater Fireball",
+    <t>"lab":"Greater Fireball",
 "des":"Fires a fireball at each character within a {#angle}° cone up to {#range} tiles in the chosen direction, dealing {#fmt} {#elm} damage each ({#formula})."</t>
   </si>
   <si>
@@ -347,18 +344,18 @@
     <t>🌋</t>
   </si>
   <si>
-    <t xml:space="preserve">"fireballvolley",
+    <t>"fireballvolley",
 "firewall"</t>
   </si>
   <si>
     <t>"range":5,"hits":[{"elm":"fire","pow":2.0,"flat":15,"src":"int"}],"cd":4,"scope":"group","w":5,"h":5,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"燃燒術",
+    <t>"lab":"燃燒術",
 "des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Combustion",
+    <t>"lab":"Combustion",
 "des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
   </si>
   <si>
@@ -374,11 +371,11 @@
     <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"流星雨",
+    <t>"lab":"流星雨",
 "des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Meteor Shower",
+    <t>"lab":"Meteor Shower",
 "des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
   </si>
   <si>
@@ -391,11 +388,11 @@
     <t>"hits":[{"elm":"ice","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"冰箭術",
+    <t>"lab":"冰箭術",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Ice Bolt",
+    <t>"lab":"Ice Bolt",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
   <si>
@@ -405,11 +402,11 @@
     <t>🧊</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"冰牆術",
+    <t>"lab":"冰牆術",
 "des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Ice Wall",
+    <t>"lab":"Ice Wall",
 "des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
   </si>
   <si>
@@ -419,18 +416,18 @@
     <t>🥶</t>
   </si>
   <si>
-    <t xml:space="preserve">"icebolt",
+    <t>"icebolt",
 "icewall"</t>
   </si>
   <si>
     <t>"hits":[{"elm":"ice","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"冰封術",
+    <t>"lab":"冰封術",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Deep Freeze",
+    <t>"lab":"Deep Freeze",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
   <si>
@@ -446,11 +443,11 @@
     <t>"hits":[{"elm":"ice","pow":2.5,"flat":20,"src":"int"}],"range":5,"cd":6</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"暴風雪",
+    <t>"lab":"暴風雪",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Blizzard",
+    <t>"lab":"Blizzard",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
   <si>
@@ -463,7 +460,7 @@
     <t>"hits":[{"elm":"poison","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毒箭術",
+    <t>"lab":"毒箭術",
 "des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
   </si>
   <si>
@@ -473,7 +470,7 @@
     <t>🌫️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毒霧術",
+    <t>"lab":"毒霧術",
 "des":"在指定區域散佈致命毒氣。"</t>
   </si>
   <si>
@@ -483,14 +480,14 @@
     <t>🍄</t>
   </si>
   <si>
-    <t xml:space="preserve">"poisondart",
+    <t>"poisondart",
 "poisonmist"</t>
   </si>
   <si>
     <t>"hits":[{"elm":"poison","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毒素引爆",
+    <t>"lab":"毒素引爆",
 "des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
   </si>
   <si>
@@ -503,11 +500,11 @@
     <t>"cd":2</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"治療",
+    <t>"lab":"治療",
 "des":"恢復目標生命值。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Heal",
+    <t>"lab":"Heal",
 "des":"恢復目標生命值。"</t>
   </si>
   <si>
@@ -520,11 +517,11 @@
     <t>"cd":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"解毒",
+    <t>"lab":"解毒",
 "des":"清除體內毒素。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Cure",
+    <t>"lab":"Cure",
 "des":"清除體內毒素。"</t>
   </si>
   <si>
@@ -534,11 +531,11 @@
     <t>☀️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"聖光",
+    <t>"lab":"聖光",
 "des":"移除 1 個負面狀態。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Holy Light",
+    <t>"lab":"Holy Light",
 "des":"移除 1 個負面狀態。"</t>
   </si>
   <si>
@@ -548,18 +545,18 @@
     <t>✨</t>
   </si>
   <si>
-    <t xml:space="preserve">"cure",
+    <t>"cure",
 "holylight"</t>
   </si>
   <si>
     <t>"cd":5</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"淨化",
+    <t>"lab":"淨化",
 "des":"清除體內毒素，移除所有負面狀態。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Purify",
+    <t>"lab":"Purify",
 "des":"清除體內毒素，移除所有負面狀態。"</t>
   </si>
   <si>
@@ -569,11 +566,11 @@
     <t>💪</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"力量增強",
+    <t>"lab":"力量增強",
 "des":"增加力量，可提升近戰傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Strength Boost",
+    <t>"lab":"Strength Boost",
 "des":"增加力量，可提升近戰傷害。"</t>
   </si>
   <si>
@@ -583,11 +580,11 @@
     <t>👟</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"敏捷增強",
+    <t>"lab":"敏捷增強",
 "des":"增加敏捷，可提升閃避。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Agility Boost",
+    <t>"lab":"Agility Boost",
 "des":"增加敏捷，可提升閃避。"</t>
   </si>
   <si>
@@ -597,32 +594,43 @@
     <t>🧠</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"智力增強",
+    <t>"lab":"智力增強",
 "des":"增加智力，可提升法術效果。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Intelligence Boost",
+    <t>"lab":"Intelligence Boost",
 "des":"增加智力，可提升法術效果。"</t>
+  </si>
+  <si>
+    <t>"scope":"cone","range":10,"angle":45,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -655,7 +663,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -954,9 +962,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -966,10 +974,11 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="64.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="67.28515625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -998,7 +1007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1019,7 +1028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1032,7 +1041,6 @@
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1040,7 +1048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1054,7 +1062,6 @@
         <v>18</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
@@ -1062,7 +1069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1072,7 +1079,6 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1"/>
       <c r="H5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1098,25 +1104,25 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="4" width="8.85546875" style="1" customWidth="1"/>
@@ -1124,10 +1130,11 @@
     <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
     <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -1172,7 +1179,6 @@
       <c r="F2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>36</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -1196,7 +1202,6 @@
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
         <v>41</v>
       </c>
@@ -1204,7 +1209,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1223,7 +1228,6 @@
       <c r="F4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
         <v>47</v>
       </c>
@@ -1231,7 +1235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>49</v>
       </c>
@@ -1254,7 +1258,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -1281,25 +1285,27 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="5" width="8.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
     <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1328,7 +1334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
@@ -1344,7 +1350,6 @@
       <c r="F2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>64</v>
       </c>
@@ -1352,7 +1357,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
@@ -1375,7 +1380,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
@@ -1402,27 +1407,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="101" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="101.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1451,7 +1458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1477,7 +1484,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" ht="105" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="105" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -1503,7 +1510,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
@@ -1520,24 +1527,24 @@
         <v>90</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1546,27 +1553,27 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>33</v>
@@ -1575,41 +1582,41 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="8:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9">
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="14" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1618,10 +1625,11 @@
     <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1650,12 +1658,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1664,22 +1672,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1688,22 +1696,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1"/>
+        <v>107</v>
+      </c>
       <c r="H3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1712,25 +1719,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" t="s">
         <v>121</v>
-      </c>
-      <c r="B5" t="s">
-        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1739,43 +1745,42 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1785,10 +1790,11 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="61" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,12 +1823,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1831,22 +1837,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1855,22 +1861,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" s="1"/>
+        <v>128</v>
+      </c>
       <c r="H3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1879,49 +1884,48 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" customHeight="1">
       <c r="F5" s="1"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1931,10 +1935,11 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1963,129 +1968,126 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>145</v>
+      </c>
       <c r="H4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -2094,10 +2096,11 @@
     <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="46" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2126,12 +2129,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2141,18 +2144,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2160,20 +2163,19 @@
       <c r="D3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2182,31 +2184,30 @@
         <v>51</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="G4" s="1"/>
       <c r="H4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="7:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9">
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="750" yWindow="1185" windowWidth="19200" windowHeight="6450" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="general" sheetId="1" r:id="rId1"/>
-    <sheet name="sword" sheetId="2" r:id="rId2"/>
-    <sheet name="archery" sheetId="3" r:id="rId3"/>
-    <sheet name="fire" sheetId="4" r:id="rId4"/>
-    <sheet name="ice" sheetId="5" r:id="rId5"/>
-    <sheet name="poison" sheetId="6" r:id="rId6"/>
-    <sheet name="support" sheetId="7" r:id="rId7"/>
-    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="general" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="sword" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="archery" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="fire" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="ice" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="poison" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="support" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="enhancement" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -59,11 +59,11 @@
     <t>passive</t>
   </si>
   <si>
-    <t>"lab":"偷竊",
+    <t xml:space="preserve">"lab":"偷竊",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
-    <t>"lab":"Stealing",
+    <t xml:space="preserve">"lab":"Stealing",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
@@ -73,11 +73,11 @@
     <t>🗝️</t>
   </si>
   <si>
-    <t>"lab":"開鎖",
+    <t xml:space="preserve">"lab":"開鎖",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
-    <t>"lab":"Lockpicking",
+    <t xml:space="preserve">"lab":"Lockpicking",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
@@ -87,11 +87,11 @@
     <t>🔪</t>
   </si>
   <si>
-    <t>"lab":"解剖",
+    <t xml:space="preserve">"lab":"解剖",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
-    <t>"lab":"Butcher",
+    <t xml:space="preserve">"lab":"Butcher",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
@@ -101,11 +101,11 @@
     <t>👤</t>
   </si>
   <si>
-    <t>"lab":"潛行",
+    <t xml:space="preserve">"lab":"潛行",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
-    <t>"lab":"Stealth",
+    <t xml:space="preserve">"lab":"Stealth",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
@@ -115,11 +115,11 @@
     <t>💰</t>
   </si>
   <si>
-    <t>"lab":"討價還價",
+    <t xml:space="preserve">"lab":"討價還價",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
-    <t>"lab":"Barter",
+    <t xml:space="preserve">"lab":"Barter",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
@@ -141,29 +141,29 @@
     <t>"hits":[{"pow":1.15,"flat":0}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t>"lab":"斬擊",
+    <t xml:space="preserve">"lab":"斬擊",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Slash",
+    <t xml:space="preserve">"lab":"Slash",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
-    <t>thrust</t>
+    <t>dash</t>
   </si>
   <si>
     <t>📍</t>
   </si>
   <si>
-    <t>"hits":[{"pow":1.0,"flat":0,"pen":0.2}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
-  </si>
-  <si>
-    <t>"lab":"刺擊",
-"des":"直線突刺。無視目標 20% 物理防禦。"</t>
-  </si>
-  <si>
-    <t>"lab":"Thrust",
-"des":"直線突刺。無視目標 20% 物理防禦。"</t>
+    <t>"hits":[{"pow":1.5,"flat":0}],"range":3,"cd":3,"scope":"dash","knock":1,"travel":{"type":"melee"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"衝刺",
+"des":"衝向敵人，造成 1.5 倍傷害並擊退 1 格。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Dash",
+"des":"Dash to an enemy, dealing 1.5x damage and knocking it back 1 tile."</t>
   </si>
   <si>
     <t>whirlwind</t>
@@ -172,17 +172,17 @@
     <t>🌪️</t>
   </si>
   <si>
-    <t>"slash","thrust"</t>
+    <t>"slash","dash"</t>
   </si>
   <si>
     <t>"range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t>"lab":"旋風斬",
+    <t xml:space="preserve">"lab":"旋風斬",
 "des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Whirlwind",
+    <t xml:space="preserve">"lab":"Whirlwind",
 "des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
   </si>
   <si>
@@ -195,15 +195,15 @@
     <t>buff</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t>"lab":"劍術專家",
+    <t xml:space="preserve">"lab":"劍術專家",
 "des":"精通劍術。裝備劍類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t>"lab":"Sword Expertise",
+    <t xml:space="preserve">"lab":"Sword Expertise",
 "des":"Mastery of swordsmanship. +10% accuracy and +10% attack power while wielding a sword."</t>
   </si>
   <si>
@@ -216,15 +216,15 @@
     <t>"swordmastery"</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t>"lab":"劍術大師",
+    <t xml:space="preserve">"lab":"劍術大師",
 "des":"劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t>"lab":"Sword Mastery",
+    <t xml:space="preserve">"lab":"Sword Mastery",
 "des":"Peak swordsmanship. Further boosts accuracy and attack power while wielding a sword."</t>
   </si>
   <si>
@@ -237,11 +237,11 @@
     <t>"hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
-    <t>"lab":"狙擊",
+    <t xml:space="preserve">"lab":"狙擊",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Snipe",
+    <t xml:space="preserve">"lab":"Snipe",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
@@ -251,15 +251,15 @@
     <t>🏹</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t>"lab":"弓箭專家",
+    <t xml:space="preserve">"lab":"弓箭專家",
 "des":"精通弓術。裝備弓類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t>"lab":"Archery Expertise",
+    <t xml:space="preserve">"lab":"Archery Expertise",
 "des":"Mastery of archery. +10% accuracy and +10% attack power while wielding a bow."</t>
   </si>
   <si>
@@ -272,15 +272,15 @@
     <t>"archeryexpert"</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t>"lab":"弓箭大師",
+    <t xml:space="preserve">"lab":"弓箭大師",
 "des":"弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t>"lab":"Archery Mastery",
+    <t xml:space="preserve">"lab":"Archery Mastery",
 "des":"Peak archery. Further boosts accuracy and attack power while wielding a bow."</t>
   </si>
   <si>
@@ -296,11 +296,11 @@
     <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","stack":3}</t>
   </si>
   <si>
-    <t>"lab":"火球術",
+    <t xml:space="preserve">"lab":"火球術",
 "des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
   </si>
   <si>
-    <t>"lab":"Fireball",
+    <t xml:space="preserve">"lab":"Fireball",
 "des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
   </si>
   <si>
@@ -316,11 +316,11 @@
     <t>"cd":3,"range":5,"cast":{},"zoneW":5,"zoneH":1,"zoneDur":4,"zoneImg":"🔥","zoneAnim":{"cell":{"size":30,"jitter":3,"scale":[0.85,1.15],"alpha":0.9,"flipX":"random"},"spawn":{"scale":{"from":0,"to":1},"duration":250,"ease":"Back.Out","stagger":70,"from":"center"},"idle":{"scaleX":{"from":0.75,"to":1.25},"scaleY":{"from":0.75,"to":1.25},"y":"-=2","duration":450,"yoyo":true,"repeat":-1,"ease":"Sine.InOut","randDelay":450},"tick":{"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"},"end":{"alpha":0,"scale":0.3,"duration":350,"ease":"Quad.In"}}</t>
   </si>
   <si>
-    <t>"lab":"火牆術",
+    <t xml:space="preserve">"lab":"火牆術",
 "des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
-    <t>"lab":"Fire Wall",
+    <t xml:space="preserve">"lab":"Fire Wall",
 "des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
@@ -330,11 +330,14 @@
     <t>"fireball"</t>
   </si>
   <si>
-    <t>"lab":"高級火球術",
+    <t>"scope":"cone","range":10,"angle":45,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"高級火球術",
 "des":"朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害({#formula})。"</t>
   </si>
   <si>
-    <t>"lab":"Greater Fireball",
+    <t xml:space="preserve">"lab":"Greater Fireball",
 "des":"Fires a fireball at each character within a {#angle}° cone up to {#range} tiles in the chosen direction, dealing {#fmt} {#elm} damage each ({#formula})."</t>
   </si>
   <si>
@@ -344,18 +347,18 @@
     <t>🌋</t>
   </si>
   <si>
-    <t>"fireballvolley",
+    <t xml:space="preserve">"fireballvolley",
 "firewall"</t>
   </si>
   <si>
     <t>"range":5,"hits":[{"elm":"fire","pow":2.0,"flat":15,"src":"int"}],"cd":4,"scope":"group","w":5,"h":5,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t>"lab":"燃燒術",
+    <t xml:space="preserve">"lab":"燃燒術",
 "des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
   </si>
   <si>
-    <t>"lab":"Combustion",
+    <t xml:space="preserve">"lab":"Combustion",
 "des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
   </si>
   <si>
@@ -371,11 +374,11 @@
     <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
   </si>
   <si>
-    <t>"lab":"流星雨",
+    <t xml:space="preserve">"lab":"流星雨",
 "des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
   </si>
   <si>
-    <t>"lab":"Meteor Shower",
+    <t xml:space="preserve">"lab":"Meteor Shower",
 "des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
   </si>
   <si>
@@ -388,11 +391,11 @@
     <t>"hits":[{"elm":"ice","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
-    <t>"lab":"冰箭術",
+    <t xml:space="preserve">"lab":"冰箭術",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
   <si>
-    <t>"lab":"Ice Bolt",
+    <t xml:space="preserve">"lab":"Ice Bolt",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
   <si>
@@ -402,11 +405,11 @@
     <t>🧊</t>
   </si>
   <si>
-    <t>"lab":"冰牆術",
+    <t xml:space="preserve">"lab":"冰牆術",
 "des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
   </si>
   <si>
-    <t>"lab":"Ice Wall",
+    <t xml:space="preserve">"lab":"Ice Wall",
 "des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
   </si>
   <si>
@@ -416,18 +419,18 @@
     <t>🥶</t>
   </si>
   <si>
-    <t>"icebolt",
+    <t xml:space="preserve">"icebolt",
 "icewall"</t>
   </si>
   <si>
     <t>"hits":[{"elm":"ice","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
-    <t>"lab":"冰封術",
+    <t xml:space="preserve">"lab":"冰封術",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
   <si>
-    <t>"lab":"Deep Freeze",
+    <t xml:space="preserve">"lab":"Deep Freeze",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
   <si>
@@ -443,11 +446,11 @@
     <t>"hits":[{"elm":"ice","pow":2.5,"flat":20,"src":"int"}],"range":5,"cd":6</t>
   </si>
   <si>
-    <t>"lab":"暴風雪",
+    <t xml:space="preserve">"lab":"暴風雪",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
   <si>
-    <t>"lab":"Blizzard",
+    <t xml:space="preserve">"lab":"Blizzard",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
   <si>
@@ -460,7 +463,7 @@
     <t>"hits":[{"elm":"poison","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
-    <t>"lab":"毒箭術",
+    <t xml:space="preserve">"lab":"毒箭術",
 "des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
   </si>
   <si>
@@ -470,7 +473,7 @@
     <t>🌫️</t>
   </si>
   <si>
-    <t>"lab":"毒霧術",
+    <t xml:space="preserve">"lab":"毒霧術",
 "des":"在指定區域散佈致命毒氣。"</t>
   </si>
   <si>
@@ -480,14 +483,14 @@
     <t>🍄</t>
   </si>
   <si>
-    <t>"poisondart",
+    <t xml:space="preserve">"poisondart",
 "poisonmist"</t>
   </si>
   <si>
     <t>"hits":[{"elm":"poison","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
-    <t>"lab":"毒素引爆",
+    <t xml:space="preserve">"lab":"毒素引爆",
 "des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
   </si>
   <si>
@@ -500,11 +503,11 @@
     <t>"cd":2</t>
   </si>
   <si>
-    <t>"lab":"治療",
+    <t xml:space="preserve">"lab":"治療",
 "des":"恢復目標生命值。"</t>
   </si>
   <si>
-    <t>"lab":"Heal",
+    <t xml:space="preserve">"lab":"Heal",
 "des":"恢復目標生命值。"</t>
   </si>
   <si>
@@ -517,11 +520,11 @@
     <t>"cd":3</t>
   </si>
   <si>
-    <t>"lab":"解毒",
+    <t xml:space="preserve">"lab":"解毒",
 "des":"清除體內毒素。"</t>
   </si>
   <si>
-    <t>"lab":"Cure",
+    <t xml:space="preserve">"lab":"Cure",
 "des":"清除體內毒素。"</t>
   </si>
   <si>
@@ -531,11 +534,11 @@
     <t>☀️</t>
   </si>
   <si>
-    <t>"lab":"聖光",
+    <t xml:space="preserve">"lab":"聖光",
 "des":"移除 1 個負面狀態。"</t>
   </si>
   <si>
-    <t>"lab":"Holy Light",
+    <t xml:space="preserve">"lab":"Holy Light",
 "des":"移除 1 個負面狀態。"</t>
   </si>
   <si>
@@ -545,18 +548,18 @@
     <t>✨</t>
   </si>
   <si>
-    <t>"cure",
+    <t xml:space="preserve">"cure",
 "holylight"</t>
   </si>
   <si>
     <t>"cd":5</t>
   </si>
   <si>
-    <t>"lab":"淨化",
+    <t xml:space="preserve">"lab":"淨化",
 "des":"清除體內毒素，移除所有負面狀態。"</t>
   </si>
   <si>
-    <t>"lab":"Purify",
+    <t xml:space="preserve">"lab":"Purify",
 "des":"清除體內毒素，移除所有負面狀態。"</t>
   </si>
   <si>
@@ -566,11 +569,11 @@
     <t>💪</t>
   </si>
   <si>
-    <t>"lab":"力量增強",
+    <t xml:space="preserve">"lab":"力量增強",
 "des":"增加力量，可提升近戰傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Strength Boost",
+    <t xml:space="preserve">"lab":"Strength Boost",
 "des":"增加力量，可提升近戰傷害。"</t>
   </si>
   <si>
@@ -580,11 +583,11 @@
     <t>👟</t>
   </si>
   <si>
-    <t>"lab":"敏捷增強",
+    <t xml:space="preserve">"lab":"敏捷增強",
 "des":"增加敏捷，可提升閃避。"</t>
   </si>
   <si>
-    <t>"lab":"Agility Boost",
+    <t xml:space="preserve">"lab":"Agility Boost",
 "des":"增加敏捷，可提升閃避。"</t>
   </si>
   <si>
@@ -594,43 +597,32 @@
     <t>🧠</t>
   </si>
   <si>
-    <t>"lab":"智力增強",
+    <t xml:space="preserve">"lab":"智力增強",
 "des":"增加智力，可提升法術效果。"</t>
   </si>
   <si>
-    <t>"lab":"Intelligence Boost",
+    <t xml:space="preserve">"lab":"Intelligence Boost",
 "des":"增加智力，可提升法術效果。"</t>
-  </si>
-  <si>
-    <t>"scope":"cone","range":10,"angle":45,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -663,7 +655,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -962,9 +954,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -974,11 +966,10 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="64.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="67.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1028,7 +1019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,7 +1039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1069,7 +1060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1086,7 +1077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1104,25 +1095,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="4" width="8.85546875" style="1" customWidth="1"/>
@@ -1130,11 +1120,10 @@
     <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
     <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1163,7 +1152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -1186,7 +1175,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -1209,7 +1198,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1235,7 +1224,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>49</v>
       </c>
@@ -1258,7 +1247,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -1285,27 +1274,25 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="5" width="8.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
     <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
@@ -1357,7 +1344,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
@@ -1380,7 +1367,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
@@ -1407,16 +1394,15 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1425,11 +1411,10 @@
     <col min="6" max="6" width="101.42578125" style="2" customWidth="1"/>
     <col min="7" max="7" width="41.5703125" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1458,7 +1443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1484,7 +1469,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="105" customHeight="1">
+    <row r="3" ht="105" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -1510,7 +1495,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
@@ -1527,24 +1512,24 @@
         <v>90</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1553,27 +1538,27 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>33</v>
@@ -1582,41 +1567,40 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1625,11 +1609,10 @@
     <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1658,12 +1641,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1672,22 +1655,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1696,21 +1679,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1719,24 +1702,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1745,42 +1728,41 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1790,11 +1772,10 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="61" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1823,12 +1804,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1837,22 +1818,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1861,21 +1842,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1884,48 +1865,47 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16.5" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F5" s="1"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1935,11 +1915,10 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1968,126 +1947,125 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -2096,11 +2074,10 @@
     <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="46" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2129,12 +2106,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2144,18 +2121,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2164,18 +2141,18 @@
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2185,29 +2162,28 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"hits":[{"pow":1.15,"flat":0}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
+    <t>"reqClass":"sword","hits":[{"pow":1.15,"flat":0}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
@@ -155,7 +155,7 @@
     <t>📍</t>
   </si>
   <si>
-    <t>"hits":[{"pow":1.5,"flat":0}],"range":3,"cd":3,"scope":"dash","knock":1,"travel":{"type":"melee"}</t>
+    <t>"reqClass":"sword","hits":[{"pow":1.5,"flat":0}],"range":3,"cd":3,"scope":"dash","knock":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"衝刺",
@@ -175,7 +175,7 @@
     <t>"slash","dash"</t>
   </si>
   <si>
-    <t>"range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
+    <t>"reqClass":"sword","range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
@@ -234,7 +234,7 @@
     <t>🎯</t>
   </si>
   <si>
-    <t>"hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
+    <t>"reqClass":"bow","hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",
@@ -1098,7 +1098,8 @@
     <row r="7" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1586,7 +1587,8 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
@@ -1749,7 +1751,8 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1891,7 +1894,8 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
@@ -2052,7 +2056,8 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
@@ -2177,7 +2182,8 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"reqClass":"sword","hits":[{"pow":1.15,"flat":0}],"range":1,"cd":1,"travel":{"type":"melee"}</t>
+    <t>"reqClass":"sword","hits":[{"pow":1.15,"flat":0}],"range":1,"scope":"arc","cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -371,7 +371,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"randomDelay":800},"fx":{"img":"🔥"},"carpet":true</t>
+    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":45,"dist":300,"scale":[2,5],"randomDelay":800},"fx":{"img":"🔥"},"minCount":5</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -371,7 +371,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":45,"dist":300,"scale":[2,5],"randomDelay":800},"fx":{"img":"🔥"},"minCount":5</t>
+    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":45,"dist":300,"scale":[1,3],"randomDelay":800},"fx":{"img":"🔥"},"minCount":5</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -371,7 +371,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":45,"dist":300,"scale":[1,3],"randomDelay":800},"fx":{"img":"🔥"},"minCount":5</t>
+    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":45,"dist":300,"scale":[1,3],"randomDelay":800},"fx":{"img":"🔥"},"minCount":7</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -371,7 +371,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":45,"dist":300,"scale":[1,3],"randomDelay":800},"fx":{"img":"🔥"},"minCount":7</t>
+    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":60,"dist":300,"scale":[2,4],"randomDelay":800},"fx":{"img":"🔥"},"minCount":10</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -371,7 +371,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":60,"dist":300,"scale":[2,4],"randomDelay":800},"fx":{"img":"🔥"},"minCount":10</t>
+    <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":60,"dist":300,"scale":[2,3.5],"randomDelay":800},"fx":{"img":"🔥"},"minCount":10</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"reqClass":"sword","hits":[{"pow":1.15,"flat":0}],"range":1,"scope":"arc","cd":1,"travel":{"type":"melee"}</t>
+    <t>"reqClass":"sword","weapon":true,"hits":[{"pow":1.15,"flat":0}],"range":1,"scope":"arc","cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
@@ -155,7 +155,7 @@
     <t>📍</t>
   </si>
   <si>
-    <t>"reqClass":"sword","hits":[{"pow":1.5,"flat":0}],"range":3,"cd":3,"scope":"dash","knock":1,"travel":{"type":"melee"}</t>
+    <t>"reqClass":"sword","weapon":true,"hits":[{"pow":1.5,"flat":0}],"range":3,"cd":3,"scope":"dash","knock":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"衝刺",
@@ -175,7 +175,7 @@
     <t>"slash","dash"</t>
   </si>
   <si>
-    <t>"reqClass":"sword","range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
+    <t>"reqClass":"sword","weapon":true,"range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
@@ -234,7 +234,7 @@
     <t>🎯</t>
   </si>
   <si>
-    <t>"reqClass":"bow","hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
+    <t>"reqClass":"bow","weapon":true,"hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -297,11 +297,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"火球術",
-"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
+"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害。{#formula}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Fireball",
-"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害({#formula})。"</t>
+"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害。{#formula}"</t>
   </si>
   <si>
     <t>firewall</t>
@@ -334,11 +334,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"高級火球術",
-"des":"朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害({#formula})。"</t>
+"des":"朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害。{#formula}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Greater Fireball",
-"des":"Fires a fireball at each character within a {#angle}° cone up to {#range} tiles in the chosen direction, dealing {#fmt} {#elm} damage each ({#formula})."</t>
+"des":"Fires a fireball at each character within a {#angle}° cone up to {#range} tiles in the chosen direction, dealing {#fmt} {#elm} damage each.{#formula}"</t>
   </si>
   <si>
     <t>combustion</t>
@@ -355,11 +355,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",
-"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
+"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害。{#formula}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Combustion",
-"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害({#formula})。"</t>
+"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害。{#formula}"</t>
   </si>
   <si>
     <t>meteorshower</t>
@@ -375,11 +375,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",
-"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
+"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害及 {#fmt1} 點{#elm1}傷害，摧毀範圍內一切。{#formula0}{#formula1}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Meteor Shower",
-"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害({#formula0})及 {#fmt1} 點{#elm1}傷害({#formula1})，摧毀範圍內一切。"</t>
+"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害及 {#fmt1} 點{#elm1}傷害，摧毀範圍內一切。{#formula0}{#formula1}"</t>
   </si>
   <si>
     <t>icebolt</t>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -142,11 +142,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
-"des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
+"des":"基本橫劈，對前方弧形範圍造成 {#fmt} 點{#elm}傷害。{#formula}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Slash",
-"des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
+"des":"A basic horizontal cut, dealing {#fmt} {#elm} damage in an arc ahead.{#formula}"</t>
   </si>
   <si>
     <t>dash</t>
@@ -159,11 +159,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"衝刺",
-"des":"衝向敵人，造成 1.5 倍傷害並擊退 1 格。"</t>
+"des":"衝向敵人，造成 {#fmt} 點{#elm}傷害並擊退 {#knock} 格。{#formula}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Dash",
-"des":"Dash to an enemy, dealing 1.5x damage and knocking it back 1 tile."</t>
+"des":"Dash to an enemy, dealing {#fmt} {#elm} damage and knocking it back {#knock} tile(s).{#formula}"</t>
   </si>
   <si>
     <t>whirlwind</t>
@@ -200,11 +200,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"劍術專家",
-"des":"精通劍術。裝備劍類武器時，命中+10%、攻擊力+10%。"</t>
+"des":"精通劍術。裝備劍類武器時，提升命中與攻擊力。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Sword Expertise",
-"des":"Mastery of swordsmanship. +10% accuracy and +10% attack power while wielding a sword."</t>
+"des":"Mastery of swordsmanship. Boosts accuracy and attack power while wielding a sword."</t>
   </si>
   <si>
     <t>swordmaster</t>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -238,11 +238,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",
-"des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
+"des":"瞄準敵人的弱點射擊，造成 {#fmt} 點{#elm}傷害。{#formula}"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Snipe",
-"des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
+"des":"Aims at an enemy's weak spot, dealing {#fmt} {#elm} damage.{#formula}"</t>
   </si>
   <si>
     <t>archeryexpert</t>
@@ -256,11 +256,11 @@
   </si>
   <si>
     <t xml:space="preserve">"lab":"弓箭專家",
-"des":"精通弓術。裝備弓類武器時，命中+10%、攻擊力+10%。"</t>
+"des":"精通弓術。裝備弓類武器時，提升命中與攻擊力。"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"Archery Expertise",
-"des":"Mastery of archery. +10% accuracy and +10% attack power while wielding a bow."</t>
+"des":"Mastery of archery. Boosts accuracy and attack power while wielding a bow."</t>
   </si>
   <si>
     <t>archerymaster</t>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -44,10 +44,10 @@
     <t>effects</t>
   </si>
   <si>
-    <t>tw</t>
-  </si>
-  <si>
-    <t>us</t>
+    <t>zh-TW</t>
+  </si>
+  <si>
+    <t>en</t>
   </si>
   <si>
     <t>steal</t>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="174">
   <si>
     <t>id</t>
   </si>
@@ -44,10 +44,10 @@
     <t>effects</t>
   </si>
   <si>
-    <t>zh-TW</t>
-  </si>
-  <si>
-    <t>en</t>
+    <t>lab</t>
+  </si>
+  <si>
+    <t>des</t>
   </si>
   <si>
     <t>steal</t>
@@ -59,12 +59,10 @@
     <t>passive</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"偷竊",
-"des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Stealing",
-"des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
+    <t>偷竊</t>
+  </si>
+  <si>
+    <t>從 NPC 或怪物身上獲取財物。成功率視敏捷而定。</t>
   </si>
   <si>
     <t>lockpick</t>
@@ -73,12 +71,10 @@
     <t>🗝️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"開鎖",
-"des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Lockpicking",
-"des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
+    <t>開鎖</t>
+  </si>
+  <si>
+    <t>破解寶箱或門鎖。解鎖更高難度的鎖具。</t>
   </si>
   <si>
     <t>butcher</t>
@@ -87,12 +83,10 @@
     <t>🔪</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"解剖",
-"des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Butcher",
-"des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
+    <t>解剖</t>
+  </si>
+  <si>
+    <t>分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。</t>
   </si>
   <si>
     <t>stealth</t>
@@ -101,12 +95,10 @@
     <t>👤</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"潛行",
-"des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Stealth",
-"des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
+    <t>潛行</t>
+  </si>
+  <si>
+    <t>進入半透明狀態，大幅降低敵方偵測範圍。</t>
   </si>
   <si>
     <t>barter</t>
@@ -115,12 +107,10 @@
     <t>💰</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"討價還價",
-"des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Barter",
-"des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
+    <t>討價還價</t>
+  </si>
+  <si>
+    <t>交易時獲得更好價格。商店售價 -15%，回收價 +15%。</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -141,12 +131,10 @@
     <t>"reqClass":"sword","weapon":true,"hits":[{"pow":1.15,"flat":0}],"range":1,"scope":"arc","cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"斬擊",
-"des":"基本橫劈，對前方弧形範圍造成 {#fmt} 點{#elm}傷害。{#formula}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Slash",
-"des":"A basic horizontal cut, dealing {#fmt} {#elm} damage in an arc ahead.{#formula}"</t>
+    <t>斬擊</t>
+  </si>
+  <si>
+    <t>基本橫劈，對前方弧形範圍造成 {#fmt} 點{#elm}傷害。{#formula}</t>
   </si>
   <si>
     <t>dash</t>
@@ -158,12 +146,10 @@
     <t>"reqClass":"sword","weapon":true,"hits":[{"pow":1.5,"flat":0}],"range":3,"cd":3,"scope":"dash","knock":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"衝刺",
-"des":"衝向敵人，造成 {#fmt} 點{#elm}傷害並擊退 {#knock} 格。{#formula}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Dash",
-"des":"Dash to an enemy, dealing {#fmt} {#elm} damage and knocking it back {#knock} tile(s).{#formula}"</t>
+    <t>衝刺</t>
+  </si>
+  <si>
+    <t>衝向敵人，造成 {#fmt} 點{#elm}傷害並擊退 {#knock} 格。{#formula}</t>
   </si>
   <si>
     <t>whirlwind</t>
@@ -178,12 +164,10 @@
     <t>"reqClass":"sword","weapon":true,"range":1,"cd":3,"scope":"group","w":3,"h":3,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"旋風斬",
-"des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Whirlwind",
-"des":"旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。"</t>
+    <t>旋風斬</t>
+  </si>
+  <si>
+    <t>旋轉劍身，對周圍範圍{#wh}方格造成多段傷害。</t>
   </si>
   <si>
     <t>swordmastery</t>
@@ -199,12 +183,10 @@
 {"type":"mod","key":"atk","m":0.1,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"劍術專家",
-"des":"精通劍術。裝備劍類武器時，提升命中與攻擊力。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Sword Expertise",
-"des":"Mastery of swordsmanship. Boosts accuracy and attack power while wielding a sword."</t>
+    <t>劍術專家</t>
+  </si>
+  <si>
+    <t>精通劍術。裝備劍類武器時，提升命中與攻擊力。</t>
   </si>
   <si>
     <t>swordmaster</t>
@@ -220,12 +202,10 @@
 {"type":"mod","key":"atk","m":0.15,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"劍術大師",
-"des":"劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Sword Mastery",
-"des":"Peak swordsmanship. Further boosts accuracy and attack power while wielding a sword."</t>
+    <t>劍術大師</t>
+  </si>
+  <si>
+    <t>劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。</t>
   </si>
   <si>
     <t>snipe</t>
@@ -237,12 +217,10 @@
     <t>"reqClass":"bow","weapon":true,"hits":[{"pow":2.5,"flat":0}],"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"狙擊",
-"des":"瞄準敵人的弱點射擊，造成 {#fmt} 點{#elm}傷害。{#formula}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Snipe",
-"des":"Aims at an enemy's weak spot, dealing {#fmt} {#elm} damage.{#formula}"</t>
+    <t>狙擊</t>
+  </si>
+  <si>
+    <t>瞄準敵人的弱點射擊，造成 {#fmt} 點{#elm}傷害。{#formula}</t>
   </si>
   <si>
     <t>archeryexpert</t>
@@ -255,12 +233,10 @@
 {"type":"mod","key":"atk","m":0.1,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓箭專家",
-"des":"精通弓術。裝備弓類武器時，提升命中與攻擊力。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Archery Expertise",
-"des":"Mastery of archery. Boosts accuracy and attack power while wielding a bow."</t>
+    <t>弓箭專家</t>
+  </si>
+  <si>
+    <t>精通弓術。裝備弓類武器時，提升命中與攻擊力。</t>
   </si>
   <si>
     <t>archerymaster</t>
@@ -276,12 +252,10 @@
 {"type":"mod","key":"atk","m":0.15,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓箭大師",
-"des":"弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Archery Mastery",
-"des":"Peak archery. Further boosts accuracy and attack power while wielding a bow."</t>
+    <t>弓箭大師</t>
+  </si>
+  <si>
+    <t>弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。</t>
   </si>
   <si>
     <t>fireball</t>
@@ -296,12 +270,10 @@
     <t>{"type":"dot","scope":"target","stage":"hit","elm":"fire","a":-5,"dur":3,"icon":"🔥","id":"burn","stack":3}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"火球術",
-"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害。{#formula}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Fireball",
-"des":"投擲火球，造成 {#fmt} 點{#elm}爆炸傷害。{#formula}"</t>
+    <t>火球術</t>
+  </si>
+  <si>
+    <t>投擲火球，造成 {#fmt} 點{#elm}爆炸傷害。{#formula}</t>
   </si>
   <si>
     <t>firewall</t>
@@ -316,12 +288,10 @@
     <t>"cd":3,"range":5,"cast":{},"zoneW":5,"zoneH":1,"zoneDur":4,"zoneImg":"🔥","zoneAnim":{"cell":{"size":30,"jitter":3,"scale":[0.85,1.15],"alpha":0.9,"flipX":"random"},"spawn":{"scale":{"from":0,"to":1},"duration":250,"ease":"Back.Out","stagger":70,"from":"center"},"idle":{"scaleX":{"from":0.75,"to":1.25},"scaleY":{"from":0.75,"to":1.25},"y":"-=2","duration":450,"yoyo":true,"repeat":-1,"ease":"Sine.InOut","randDelay":450},"tick":{"scale":{"from":1,"to":1.4},"duration":150,"yoyo":true,"ease":"Quad.Out"},"end":{"alpha":0,"scale":0.3,"duration":350,"ease":"Quad.In"}}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"火牆術",
-"des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Fire Wall",
-"des":"召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。"</t>
+    <t>火牆術</t>
+  </si>
+  <si>
+    <t>召喚{#wh}方格的火焰地帶。對經過者施加持續灼燒。</t>
   </si>
   <si>
     <t>fireballvolley</t>
@@ -333,12 +303,10 @@
     <t>"scope":"cone","range":10,"angle":45,"hits":[{"elm":"fire","pow":1.8,"flat":10,"src":"int"}],"cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"高級火球術",
-"des":"朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害。{#formula}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Greater Fireball",
-"des":"Fires a fireball at each character within a {#angle}° cone up to {#range} tiles in the chosen direction, dealing {#fmt} {#elm} damage each.{#formula}"</t>
+    <t>高級火球術</t>
+  </si>
+  <si>
+    <t>朝指定方向 {#angle}° 扇形、{#range} 格內的每個角色各自發射火球，每發造成 {#fmt} 點{#elm}傷害。{#formula}</t>
   </si>
   <si>
     <t>combustion</t>
@@ -354,12 +322,10 @@
     <t>"range":5,"hits":[{"elm":"fire","pow":2.0,"flat":15,"src":"int"}],"cd":4,"scope":"group","w":5,"h":5,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"燃燒術",
-"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害。{#formula}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Combustion",
-"des":"引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害。{#formula}"</t>
+    <t>燃燒術</t>
+  </si>
+  <si>
+    <t>引爆範圍{#wh}方格內目標身上的灼燒狀態，造成 {#fmt} 點{#elm}瞬間大傷害。{#formula}</t>
   </si>
   <si>
     <t>meteorshower</t>
@@ -374,12 +340,10 @@
     <t>"hits":[{"elm":"fire","pow":2.5,"flat":20,"src":"int"},{"elm":"phy","pow":2,"flat":10,"src":"int"}],"range":5,"cd":6,"scope":"area","w":7,"h":7,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135,"angle":60,"dist":300,"scale":[2,3.5],"randomDelay":800},"fx":{"img":"🔥"},"minCount":10</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"流星雨",
-"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害及 {#fmt1} 點{#elm1}傷害，摧毀範圍內一切。{#formula0}{#formula1}"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Meteor Shower",
-"des":"大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害及 {#fmt1} 點{#elm1}傷害，摧毀範圍內一切。{#formula0}{#formula1}"</t>
+    <t>流星雨</t>
+  </si>
+  <si>
+    <t>大範圍{#wh}方格隕石轟炸，每顆造成 {#fmt0} 點{#elm0}傷害及 {#fmt1} 點{#elm1}傷害，摧毀範圍內一切。{#formula0}{#formula1}</t>
   </si>
   <si>
     <t>icebolt</t>
@@ -391,12 +355,10 @@
     <t>"hits":[{"elm":"ice","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"冰箭術",
-"des":"單體冰錐。造成傷害並減速 30%。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Ice Bolt",
-"des":"單體冰錐。造成傷害並減速 30%。"</t>
+    <t>冰箭術</t>
+  </si>
+  <si>
+    <t>單體冰錐。造成傷害並減速 30%。</t>
   </si>
   <si>
     <t>icewall</t>
@@ -405,12 +367,10 @@
     <t>🧊</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"冰牆術",
-"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Ice Wall",
-"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
+    <t>冰牆術</t>
+  </si>
+  <si>
+    <t>召喚可抵擋飛行道具的冰塊物理障礙物。</t>
   </si>
   <si>
     <t>deepfreeze</t>
@@ -426,12 +386,10 @@
     <t>"hits":[{"elm":"ice","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"冰封術",
-"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Deep Freeze",
-"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
+    <t>冰封術</t>
+  </si>
+  <si>
+    <t>將減速狀態轉為凍結，使敵方完全無法行動 3 秒。</t>
   </si>
   <si>
     <t>blizzard</t>
@@ -446,12 +404,10 @@
     <t>"hits":[{"elm":"ice","pow":2.5,"flat":20,"src":"int"}],"range":5,"cd":6</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"暴風雪",
-"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Blizzard",
-"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
+    <t>暴風雪</t>
+  </si>
+  <si>
+    <t>大範圍持續性傷害，並有 10% 機率直接凍結敵人。</t>
   </si>
   <si>
     <t>poisondart</t>
@@ -463,8 +419,10 @@
     <t>"hits":[{"elm":"poison","pow":1.5,"flat":10,"src":"int"}],"range":5,"cd":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毒箭術",
-"des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
+    <t>毒箭術</t>
+  </si>
+  <si>
+    <t>遠程發射毒針，使目標進入每秒扣血的中毒狀態。</t>
   </si>
   <si>
     <t>poisonmist</t>
@@ -473,8 +431,10 @@
     <t>🌫️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毒霧術",
-"des":"在指定區域散佈致命毒氣。"</t>
+    <t>毒霧術</t>
+  </si>
+  <si>
+    <t>在指定區域散佈致命毒氣。</t>
   </si>
   <si>
     <t>venomburst</t>
@@ -490,8 +450,10 @@
     <t>"hits":[{"elm":"poison","pow":2.0,"flat":15,"src":"int"}],"range":5,"cd":4</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"毒素引爆",
-"des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
+    <t>毒素引爆</t>
+  </si>
+  <si>
+    <t>使受毒者爆炸，將毒素噴濺至周圍目標。</t>
   </si>
   <si>
     <t>heal</t>
@@ -503,12 +465,10 @@
     <t>"cd":2</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"治療",
-"des":"恢復目標生命值。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Heal",
-"des":"恢復目標生命值。"</t>
+    <t>治療</t>
+  </si>
+  <si>
+    <t>恢復目標生命值。</t>
   </si>
   <si>
     <t>cure</t>
@@ -520,12 +480,10 @@
     <t>"cd":3</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"解毒",
-"des":"清除體內毒素。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Cure",
-"des":"清除體內毒素。"</t>
+    <t>解毒</t>
+  </si>
+  <si>
+    <t>清除體內毒素。</t>
   </si>
   <si>
     <t>holylight</t>
@@ -534,12 +492,10 @@
     <t>☀️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"聖光",
-"des":"移除 1 個負面狀態。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Holy Light",
-"des":"移除 1 個負面狀態。"</t>
+    <t>聖光</t>
+  </si>
+  <si>
+    <t>移除 1 個負面狀態。</t>
   </si>
   <si>
     <t>purify</t>
@@ -555,12 +511,10 @@
     <t>"cd":5</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"淨化",
-"des":"清除體內毒素，移除所有負面狀態。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Purify",
-"des":"清除體內毒素，移除所有負面狀態。"</t>
+    <t>淨化</t>
+  </si>
+  <si>
+    <t>清除體內毒素，移除所有負面狀態。</t>
   </si>
   <si>
     <t>strboost</t>
@@ -569,12 +523,10 @@
     <t>💪</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"力量增強",
-"des":"增加力量，可提升近戰傷害。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Strength Boost",
-"des":"增加力量，可提升近戰傷害。"</t>
+    <t>力量增強</t>
+  </si>
+  <si>
+    <t>增加力量，可提升近戰傷害。</t>
   </si>
   <si>
     <t>agiboost</t>
@@ -583,12 +535,10 @@
     <t>👟</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"敏捷增強",
-"des":"增加敏捷，可提升閃避。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Agility Boost",
-"des":"增加敏捷，可提升閃避。"</t>
+    <t>敏捷增強</t>
+  </si>
+  <si>
+    <t>增加敏捷，可提升閃避。</t>
   </si>
   <si>
     <t>intboost</t>
@@ -597,12 +547,10 @@
     <t>🧠</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"智力增強",
-"des":"增加智力，可提升法術效果。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Intelligence Boost",
-"des":"增加智力，可提升法術效果。"</t>
+    <t>智力增強</t>
+  </si>
+  <si>
+    <t>增加智力，可提升法術效果。</t>
   </si>
 </sst>
 </file>
@@ -1098,11 +1046,13 @@
     <row r="7" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1587,11 +1537,13 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1751,11 +1703,13 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1828,15 +1782,15 @@
         <v>130</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1848,18 +1802,18 @@
         <v>129</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1868,16 +1822,16 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1894,11 +1848,13 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1953,98 +1909,98 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -2056,11 +2012,13 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2113,10 +2071,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2126,18 +2084,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2146,18 +2104,18 @@
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2167,10 +2125,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">
@@ -2182,11 +2140,13 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
